--- a/artfynd/A 41573-2024 artfynd.xlsx
+++ b/artfynd/A 41573-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122901183</v>
+        <v>122901216</v>
       </c>
       <c r="B2" t="n">
         <v>95128</v>
@@ -710,12 +710,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -727,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>589286</v>
+        <v>589279</v>
       </c>
       <c r="R2" t="n">
-        <v>6415786</v>
+        <v>6415793</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -763,11 +763,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-05</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ett flertal i närheten</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -914,7 +909,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122901300</v>
+        <v>122902684</v>
       </c>
       <c r="B4" t="n">
         <v>98357</v>
@@ -947,36 +942,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kärrebo 1:6, Sm</t>
+          <t>A 41571, Kärrebo, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>589280</v>
+        <v>589293</v>
       </c>
       <c r="R4" t="n">
-        <v>6415806</v>
+        <v>6415810</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1021,19 +1008,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Gunilla Nilsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122901216</v>
+        <v>122901183</v>
       </c>
       <c r="B5" t="n">
         <v>95128</v>
@@ -1068,12 +1055,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -1085,10 +1072,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>589279</v>
+        <v>589286</v>
       </c>
       <c r="R5" t="n">
-        <v>6415793</v>
+        <v>6415786</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1121,6 +1108,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-05</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ett flertal i närheten</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1148,7 +1140,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122902684</v>
+        <v>122901300</v>
       </c>
       <c r="B6" t="n">
         <v>98357</v>
@@ -1181,28 +1173,36 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>A 41571, Kärrebo, Sm</t>
+          <t>Kärrebo 1:6, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>589293</v>
+        <v>589280</v>
       </c>
       <c r="R6" t="n">
-        <v>6415810</v>
+        <v>6415806</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1247,12 +1247,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Gunilla Nilsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Gunilla Nilsson</t>
+          <t>Gunilla Nilsson, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 41573-2024 artfynd.xlsx
+++ b/artfynd/A 41573-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122901216</v>
+        <v>122902684</v>
       </c>
       <c r="B2" t="n">
-        <v>95128</v>
+        <v>98357</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -723,17 +719,17 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kärrebo 1:6, Sm</t>
+          <t>A 41571, Kärrebo, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>589279</v>
+        <v>589293</v>
       </c>
       <c r="R2" t="n">
-        <v>6415793</v>
+        <v>6415810</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -778,22 +774,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Gunilla Nilsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122901257</v>
+        <v>122901216</v>
       </c>
       <c r="B3" t="n">
-        <v>98357</v>
+        <v>95128</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,42 +798,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
@@ -846,10 +838,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>589276</v>
+        <v>589279</v>
       </c>
       <c r="R3" t="n">
-        <v>6415800</v>
+        <v>6415793</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -909,7 +901,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122902684</v>
+        <v>122901257</v>
       </c>
       <c r="B4" t="n">
         <v>98357</v>
@@ -942,28 +934,36 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>A 41571, Kärrebo, Sm</t>
+          <t>Kärrebo 1:6, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>589293</v>
+        <v>589276</v>
       </c>
       <c r="R4" t="n">
-        <v>6415810</v>
+        <v>6415800</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1008,22 +1008,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Gunilla Nilsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Gunilla Nilsson</t>
+          <t>Gunilla Nilsson, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122901183</v>
+        <v>122901300</v>
       </c>
       <c r="B5" t="n">
-        <v>95128</v>
+        <v>98357</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,38 +1032,42 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
@@ -1072,10 +1076,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>589286</v>
+        <v>589280</v>
       </c>
       <c r="R5" t="n">
-        <v>6415786</v>
+        <v>6415806</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1110,11 +1114,6 @@
           <t>2025-03-05</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ett flertal i närheten</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1133,17 +1132,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Gunilla Nilsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122901300</v>
+        <v>122901183</v>
       </c>
       <c r="B6" t="n">
-        <v>98357</v>
+        <v>95128</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1152,42 +1151,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
@@ -1196,10 +1191,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>589280</v>
+        <v>589286</v>
       </c>
       <c r="R6" t="n">
-        <v>6415806</v>
+        <v>6415786</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1232,6 +1227,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-05</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ett flertal i närheten</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 41573-2024 artfynd.xlsx
+++ b/artfynd/A 41573-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122902684</v>
+        <v>122901183</v>
       </c>
       <c r="B2" t="n">
-        <v>98357</v>
+        <v>95136</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,31 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -719,17 +723,17 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>A 41571, Kärrebo, Sm</t>
+          <t>Kärrebo 1:6, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>589293</v>
+        <v>589286</v>
       </c>
       <c r="R2" t="n">
-        <v>6415810</v>
+        <v>6415786</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,6 +763,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-05</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ett flertal i närheten</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,22 +783,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Gunilla Nilsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Gunilla Nilsson</t>
+          <t>Gunilla Nilsson, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122901216</v>
+        <v>122901257</v>
       </c>
       <c r="B3" t="n">
-        <v>95128</v>
+        <v>98365</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,38 +807,42 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
@@ -838,10 +851,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>589279</v>
+        <v>589276</v>
       </c>
       <c r="R3" t="n">
-        <v>6415793</v>
+        <v>6415800</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -901,10 +914,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122901257</v>
+        <v>122902684</v>
       </c>
       <c r="B4" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -934,36 +947,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kärrebo 1:6, Sm</t>
+          <t>A 41571, Kärrebo, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>589276</v>
+        <v>589293</v>
       </c>
       <c r="R4" t="n">
-        <v>6415800</v>
+        <v>6415810</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1008,22 +1013,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Gunilla Nilsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122901300</v>
+        <v>122901216</v>
       </c>
       <c r="B5" t="n">
-        <v>98357</v>
+        <v>95136</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,42 +1037,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
@@ -1076,10 +1077,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>589280</v>
+        <v>589279</v>
       </c>
       <c r="R5" t="n">
-        <v>6415806</v>
+        <v>6415793</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1132,17 +1133,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Gunilla Nilsson</t>
+          <t>Gunilla Nilsson, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122901183</v>
+        <v>122901300</v>
       </c>
       <c r="B6" t="n">
-        <v>95128</v>
+        <v>98365</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1151,38 +1152,42 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
@@ -1191,10 +1196,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>589286</v>
+        <v>589280</v>
       </c>
       <c r="R6" t="n">
-        <v>6415786</v>
+        <v>6415806</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1229,11 +1234,6 @@
           <t>2025-03-05</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ett flertal i närheten</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Gunilla Nilsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 41573-2024 artfynd.xlsx
+++ b/artfynd/A 41573-2024 artfynd.xlsx
@@ -795,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122901257</v>
+        <v>122901216</v>
       </c>
       <c r="B3" t="n">
-        <v>98365</v>
+        <v>95136</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,42 +807,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
@@ -851,10 +847,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>589276</v>
+        <v>589279</v>
       </c>
       <c r="R3" t="n">
-        <v>6415800</v>
+        <v>6415793</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -914,7 +910,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122902684</v>
+        <v>122901257</v>
       </c>
       <c r="B4" t="n">
         <v>98365</v>
@@ -947,28 +943,36 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>A 41571, Kärrebo, Sm</t>
+          <t>Kärrebo 1:6, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>589293</v>
+        <v>589276</v>
       </c>
       <c r="R4" t="n">
-        <v>6415810</v>
+        <v>6415800</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1013,22 +1017,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Gunilla Nilsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Gunilla Nilsson</t>
+          <t>Gunilla Nilsson, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122901216</v>
+        <v>122901300</v>
       </c>
       <c r="B5" t="n">
-        <v>95136</v>
+        <v>98365</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1037,38 +1041,42 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
@@ -1077,10 +1085,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>589279</v>
+        <v>589280</v>
       </c>
       <c r="R5" t="n">
-        <v>6415793</v>
+        <v>6415806</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1140,7 +1148,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122901300</v>
+        <v>122902684</v>
       </c>
       <c r="B6" t="n">
         <v>98365</v>
@@ -1173,36 +1181,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kärrebo 1:6, Sm</t>
+          <t>A 41571, Kärrebo, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>589280</v>
+        <v>589293</v>
       </c>
       <c r="R6" t="n">
-        <v>6415806</v>
+        <v>6415810</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">

--- a/artfynd/A 41573-2024 artfynd.xlsx
+++ b/artfynd/A 41573-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122901183</v>
+        <v>122901300</v>
       </c>
       <c r="B2" t="n">
-        <v>95136</v>
+        <v>98365</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,42 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
@@ -727,10 +731,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>589286</v>
+        <v>589280</v>
       </c>
       <c r="R2" t="n">
-        <v>6415786</v>
+        <v>6415806</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -765,11 +769,6 @@
           <t>2025-03-05</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ett flertal i närheten</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -788,17 +787,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Gunilla Nilsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122901216</v>
+        <v>122902684</v>
       </c>
       <c r="B3" t="n">
-        <v>95136</v>
+        <v>98365</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,35 +806,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -843,17 +838,17 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kärrebo 1:6, Sm</t>
+          <t>A 41571, Kärrebo, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>589279</v>
+        <v>589293</v>
       </c>
       <c r="R3" t="n">
-        <v>6415793</v>
+        <v>6415810</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -898,12 +893,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Gunilla Nilsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -1029,10 +1024,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122901300</v>
+        <v>122901183</v>
       </c>
       <c r="B5" t="n">
-        <v>98365</v>
+        <v>95136</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1041,42 +1036,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
@@ -1085,10 +1076,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>589280</v>
+        <v>589286</v>
       </c>
       <c r="R5" t="n">
-        <v>6415806</v>
+        <v>6415786</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1121,6 +1112,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-05</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ett flertal i närheten</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1148,10 +1144,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122902684</v>
+        <v>122901216</v>
       </c>
       <c r="B6" t="n">
-        <v>98365</v>
+        <v>95136</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1160,31 +1156,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -1192,17 +1192,17 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>A 41571, Kärrebo, Sm</t>
+          <t>Kärrebo 1:6, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>589293</v>
+        <v>589279</v>
       </c>
       <c r="R6" t="n">
-        <v>6415810</v>
+        <v>6415793</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1247,12 +1247,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Gunilla Nilsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Gunilla Nilsson</t>
+          <t>Gunilla Nilsson, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 41573-2024 artfynd.xlsx
+++ b/artfynd/A 41573-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122901300</v>
+        <v>122901183</v>
       </c>
       <c r="B2" t="n">
-        <v>98365</v>
+        <v>95136</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,42 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
@@ -731,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>589280</v>
+        <v>589286</v>
       </c>
       <c r="R2" t="n">
-        <v>6415806</v>
+        <v>6415786</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -769,6 +765,11 @@
           <t>2025-03-05</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ett flertal i närheten</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -787,14 +788,14 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Gunilla Nilsson</t>
+          <t>Gunilla Nilsson, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122902684</v>
+        <v>122901300</v>
       </c>
       <c r="B3" t="n">
         <v>98365</v>
@@ -827,28 +828,36 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>A 41571, Kärrebo, Sm</t>
+          <t>Kärrebo 1:6, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>589293</v>
+        <v>589280</v>
       </c>
       <c r="R3" t="n">
-        <v>6415810</v>
+        <v>6415806</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -893,7 +902,7 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Gunilla Nilsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
@@ -1024,10 +1033,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122901183</v>
+        <v>122902684</v>
       </c>
       <c r="B5" t="n">
-        <v>95136</v>
+        <v>98365</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,35 +1045,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -1072,17 +1077,17 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kärrebo 1:6, Sm</t>
+          <t>A 41571, Kärrebo, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>589286</v>
+        <v>589293</v>
       </c>
       <c r="R5" t="n">
-        <v>6415786</v>
+        <v>6415810</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1112,11 +1117,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-05</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ett flertal i närheten</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1132,12 +1132,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Gunilla Nilsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 41573-2024 artfynd.xlsx
+++ b/artfynd/A 41573-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122901183</v>
+        <v>122902684</v>
       </c>
       <c r="B2" t="n">
-        <v>95136</v>
+        <v>98368</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -723,17 +719,17 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kärrebo 1:6, Sm</t>
+          <t>A 41571, Kärrebo, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>589286</v>
+        <v>589293</v>
       </c>
       <c r="R2" t="n">
-        <v>6415786</v>
+        <v>6415810</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -763,11 +759,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-05</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ett flertal i närheten</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -783,22 +774,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Gunilla Nilsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122901300</v>
+        <v>122901183</v>
       </c>
       <c r="B3" t="n">
-        <v>98365</v>
+        <v>95139</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,42 +798,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
@@ -851,10 +838,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>589280</v>
+        <v>589286</v>
       </c>
       <c r="R3" t="n">
-        <v>6415806</v>
+        <v>6415786</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -889,6 +876,11 @@
           <t>2025-03-05</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ett flertal i närheten</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -907,7 +899,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Gunilla Nilsson</t>
+          <t>Gunilla Nilsson, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -917,7 +909,7 @@
         <v>122901257</v>
       </c>
       <c r="B4" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1033,10 +1025,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122902684</v>
+        <v>122901300</v>
       </c>
       <c r="B5" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1066,28 +1058,36 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>A 41571, Kärrebo, Sm</t>
+          <t>Kärrebo 1:6, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>589293</v>
+        <v>589280</v>
       </c>
       <c r="R5" t="n">
-        <v>6415810</v>
+        <v>6415806</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Gunilla Nilsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
@@ -1147,7 +1147,7 @@
         <v>122901216</v>
       </c>
       <c r="B6" t="n">
-        <v>95136</v>
+        <v>95139</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 41573-2024 artfynd.xlsx
+++ b/artfynd/A 41573-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122902684</v>
+        <v>122901257</v>
       </c>
       <c r="B2" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -708,28 +708,36 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>A 41571, Kärrebo, Sm</t>
+          <t>Kärrebo 1:6, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>589293</v>
+        <v>589276</v>
       </c>
       <c r="R2" t="n">
-        <v>6415810</v>
+        <v>6415800</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -774,12 +782,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Gunilla Nilsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Gunilla Nilsson</t>
+          <t>Gunilla Nilsson, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -789,7 +797,7 @@
         <v>122901183</v>
       </c>
       <c r="B3" t="n">
-        <v>95139</v>
+        <v>95141</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -906,10 +914,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122901257</v>
+        <v>122901300</v>
       </c>
       <c r="B4" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -941,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -962,10 +970,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>589276</v>
+        <v>589280</v>
       </c>
       <c r="R4" t="n">
-        <v>6415800</v>
+        <v>6415806</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1018,17 +1026,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Gunilla Nilsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122901300</v>
+        <v>122902684</v>
       </c>
       <c r="B5" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1058,36 +1066,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kärrebo 1:6, Sm</t>
+          <t>A 41571, Kärrebo, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>589280</v>
+        <v>589293</v>
       </c>
       <c r="R5" t="n">
-        <v>6415806</v>
+        <v>6415810</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
@@ -1147,7 +1147,7 @@
         <v>122901216</v>
       </c>
       <c r="B6" t="n">
-        <v>95139</v>
+        <v>95141</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 41573-2024 artfynd.xlsx
+++ b/artfynd/A 41573-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122901257</v>
+        <v>122901300</v>
       </c>
       <c r="B2" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -731,10 +731,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>589276</v>
+        <v>589280</v>
       </c>
       <c r="R2" t="n">
-        <v>6415800</v>
+        <v>6415806</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -787,17 +787,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Gunilla Nilsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122901183</v>
+        <v>122902684</v>
       </c>
       <c r="B3" t="n">
-        <v>95141</v>
+        <v>98376</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,35 +806,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -842,17 +838,17 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kärrebo 1:6, Sm</t>
+          <t>A 41571, Kärrebo, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>589286</v>
+        <v>589293</v>
       </c>
       <c r="R3" t="n">
-        <v>6415786</v>
+        <v>6415810</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -882,11 +878,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-05</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ett flertal i närheten</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,22 +893,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Gunilla Nilsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122901300</v>
+        <v>122901183</v>
       </c>
       <c r="B4" t="n">
-        <v>98370</v>
+        <v>95147</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -926,42 +917,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
@@ -970,10 +957,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>589280</v>
+        <v>589286</v>
       </c>
       <c r="R4" t="n">
-        <v>6415806</v>
+        <v>6415786</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1008,6 +995,11 @@
           <t>2025-03-05</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ett flertal i närheten</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1026,17 +1018,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Gunilla Nilsson</t>
+          <t>Gunilla Nilsson, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122902684</v>
+        <v>122901257</v>
       </c>
       <c r="B5" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1066,28 +1058,36 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>A 41571, Kärrebo, Sm</t>
+          <t>Kärrebo 1:6, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>589293</v>
+        <v>589276</v>
       </c>
       <c r="R5" t="n">
-        <v>6415810</v>
+        <v>6415800</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1132,12 +1132,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Gunilla Nilsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Gunilla Nilsson</t>
+          <t>Gunilla Nilsson, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1147,7 +1147,7 @@
         <v>122901216</v>
       </c>
       <c r="B6" t="n">
-        <v>95141</v>
+        <v>95147</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 41573-2024 artfynd.xlsx
+++ b/artfynd/A 41573-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122901300</v>
+        <v>122901257</v>
       </c>
       <c r="B2" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -731,10 +731,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>589280</v>
+        <v>589276</v>
       </c>
       <c r="R2" t="n">
-        <v>6415806</v>
+        <v>6415800</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -787,17 +787,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Gunilla Nilsson</t>
+          <t>Gunilla Nilsson, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122902684</v>
+        <v>122901183</v>
       </c>
       <c r="B3" t="n">
-        <v>98376</v>
+        <v>95150</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,31 +806,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -838,17 +842,17 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>A 41571, Kärrebo, Sm</t>
+          <t>Kärrebo 1:6, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>589293</v>
+        <v>589286</v>
       </c>
       <c r="R3" t="n">
-        <v>6415810</v>
+        <v>6415786</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -878,6 +882,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-05</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ett flertal i närheten</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,22 +902,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Gunilla Nilsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Gunilla Nilsson</t>
+          <t>Gunilla Nilsson, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122901183</v>
+        <v>122902684</v>
       </c>
       <c r="B4" t="n">
-        <v>95147</v>
+        <v>98379</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -917,35 +926,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -953,17 +958,17 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kärrebo 1:6, Sm</t>
+          <t>A 41571, Kärrebo, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>589286</v>
+        <v>589293</v>
       </c>
       <c r="R4" t="n">
-        <v>6415786</v>
+        <v>6415810</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -993,11 +998,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-05</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ett flertal i närheten</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1013,22 +1013,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Gunilla Nilsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122901257</v>
+        <v>122901300</v>
       </c>
       <c r="B5" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1081,10 +1081,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>589276</v>
+        <v>589280</v>
       </c>
       <c r="R5" t="n">
-        <v>6415800</v>
+        <v>6415806</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Gunilla Nilsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1147,7 +1147,7 @@
         <v>122901216</v>
       </c>
       <c r="B6" t="n">
-        <v>95147</v>
+        <v>95150</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 41573-2024 artfynd.xlsx
+++ b/artfynd/A 41573-2024 artfynd.xlsx
@@ -1147,7 +1147,7 @@
         <v>122901216</v>
       </c>
       <c r="B6" t="n">
-        <v>95150</v>
+        <v>95167</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 41573-2024 artfynd.xlsx
+++ b/artfynd/A 41573-2024 artfynd.xlsx
@@ -1147,7 +1147,7 @@
         <v>122901216</v>
       </c>
       <c r="B6" t="n">
-        <v>95167</v>
+        <v>95173</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 41573-2024 artfynd.xlsx
+++ b/artfynd/A 41573-2024 artfynd.xlsx
@@ -1147,7 +1147,7 @@
         <v>122901216</v>
       </c>
       <c r="B6" t="n">
-        <v>95173</v>
+        <v>95175</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 41573-2024 artfynd.xlsx
+++ b/artfynd/A 41573-2024 artfynd.xlsx
@@ -1147,7 +1147,7 @@
         <v>122901216</v>
       </c>
       <c r="B6" t="n">
-        <v>95175</v>
+        <v>95683</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
